--- a/public/downloads/KaiData-driven2022.xlsx
+++ b/public/downloads/KaiData-driven2022.xlsx
@@ -1596,16 +1596,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1555725550688343</v>
+        <v>-0.2064281848268426</v>
       </c>
       <c r="O3" s="5">
         <v>64</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7347901663431785</v>
+        <v>0.742408060568538</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1347437320233994</v>
+        <v>0.1300079875251447</v>
       </c>
       <c r="R3" s="5">
         <v>63</v>
@@ -1655,16 +1655,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1447981726984653</v>
+        <v>0.1536271719251658</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1172601822361117</v>
+        <v>0.1165480392424545</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1172601822361117</v>
+        <v>0.1165480392424545</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -1714,16 +1714,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2821240692397194</v>
+        <v>0.3090583683340142</v>
       </c>
       <c r="O5" s="5">
         <v>34</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2771004225335371</v>
+        <v>0.2742803671039928</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.271810311506582</v>
+        <v>0.2704087409984937</v>
       </c>
       <c r="R5" s="5">
         <v>34</v>
@@ -1773,13 +1773,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.69339624912814</v>
+        <v>0.6893628583257048</v>
       </c>
       <c r="O6" s="5">
         <v>18</v>
       </c>
       <c r="P6" s="4">
-        <v>9.29234816529927</v>
+        <v>9.294364860700489</v>
       </c>
       <c r="Q6" s="4">
         <v>0.2860965185222659</v>
@@ -1832,16 +1832,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2638736821063081</v>
+        <v>0.2715062724240802</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1431005381089219</v>
+        <v>0.1428178495786341</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1431005381089219</v>
+        <v>0.1428178495786341</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -1891,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1338487767278721</v>
+        <v>-0.1409954083309231</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -1950,16 +1950,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.5288375434798004</v>
+        <v>0.7813470984696806</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5749254209561481</v>
+        <v>0.5468688037350502</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5749254209561481</v>
+        <v>0.5468688037350502</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -2009,16 +2009,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.0907930816235923</v>
+        <v>-0.1539910074606894</v>
       </c>
       <c r="O10" s="5">
         <v>9</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1133981451414657</v>
+        <v>0.1063761533817882</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1133981451414657</v>
+        <v>0.1063761533817882</v>
       </c>
       <c r="R10" s="5">
         <v>9</v>
@@ -2068,13 +2068,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.09074296876976717</v>
+        <v>-0.1201676565856218</v>
       </c>
       <c r="O11" s="5">
         <v>8</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1587643033754465</v>
+        <v>0.1554948936181293</v>
       </c>
       <c r="Q11" s="4">
         <v>0.1428157407130186</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.1239513565840614</v>
+        <v>-0.2137302449848448</v>
       </c>
       <c r="O12" s="5">
         <v>9</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2041991689849248</v>
+        <v>0.1942237369403933</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2041991689849248</v>
+        <v>0.1942237369403933</v>
       </c>
       <c r="R12" s="5">
         <v>9</v>
@@ -2186,16 +2186,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.07550500671550095</v>
+        <v>0.1644366520997096</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3301320528186837</v>
+        <v>0.320250758887105</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3301320528186837</v>
+        <v>0.320250758887105</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.2909150136190506</v>
+        <v>0.2422611742816798</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1634197074043681</v>
+        <v>0.1580137252557713</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1634197074043681</v>
+        <v>0.1580137252557713</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -2304,16 +2304,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.1831997189496077</v>
+        <v>-0.1956641215423645</v>
       </c>
       <c r="O15" s="5">
         <v>9</v>
       </c>
       <c r="P15" s="4">
-        <v>0.1174896120449538</v>
+        <v>0.1161046784235364</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.1174896120449538</v>
+        <v>0.1161046784235364</v>
       </c>
       <c r="R15" s="5">
         <v>9</v>
@@ -2363,13 +2363,13 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.3074838668780684</v>
+        <v>-0.3099475953753767</v>
       </c>
       <c r="O16" s="5">
         <v>8</v>
       </c>
       <c r="P16" s="4">
-        <v>0.06562064926754581</v>
+        <v>0.06534690165673378</v>
       </c>
       <c r="Q16" s="4">
         <v>0.05862839280109355</v>
@@ -2422,16 +2422,16 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>0.09548340105622542</v>
+        <v>0.1010290592512977</v>
       </c>
       <c r="O17" s="5">
         <v>9</v>
       </c>
       <c r="P17" s="4">
-        <v>0.07496020805994962</v>
+        <v>0.07434402381605271</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.07496020805994962</v>
+        <v>0.07434402381605271</v>
       </c>
       <c r="R17" s="5">
         <v>9</v>
@@ -2481,16 +2481,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.7307599738275039</v>
+        <v>0.819665876302281</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2754110471551032</v>
+        <v>0.2655326135467946</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2754110471551032</v>
+        <v>0.2655326135467946</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -2663,16 +2663,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2372956180916801</v>
+        <v>0.1161377777293637</v>
       </c>
       <c r="O3" s="5">
         <v>79</v>
       </c>
       <c r="P3" s="4">
-        <v>0.502263989543528</v>
+        <v>0.4998383153346897</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4946092044345844</v>
+        <v>0.4890548336543245</v>
       </c>
       <c r="R3" s="5">
         <v>79</v>
@@ -2722,16 +2722,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.06912553041423071</v>
+        <v>0.1122925699999939</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.192678658738932</v>
+        <v>0.1904729663464097</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.192678658738932</v>
+        <v>0.1904729663464097</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -2781,16 +2781,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4792303057901554</v>
+        <v>0.3485470325000009</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.490934094071996</v>
+        <v>0.4572416610731512</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4630804237613261</v>
+        <v>0.4435882442968949</v>
       </c>
       <c r="R5" s="5">
         <v>22</v>
@@ -2840,7 +2840,7 @@
         <v>34</v>
       </c>
       <c r="N6" s="4">
-        <v>6.489986403748371</v>
+        <v>6.306678359760738</v>
       </c>
       <c r="O6" s="5">
         <v>36</v>
@@ -2897,16 +2897,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.7032448929891922</v>
+        <v>0.683819433374083</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2288222662603435</v>
+        <v>0.2281028047931173</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2288222662603435</v>
+        <v>0.2281028047931173</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.4678451895498007</v>
+        <v>-0.4753224490820145</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -3015,16 +3015,16 @@
         <v>6</v>
       </c>
       <c r="N9" s="4">
-        <v>2.179554872322134</v>
+        <v>2.401710306230598</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5610750684660177</v>
+        <v>0.5363911313650773</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5610750684660177</v>
+        <v>0.5363911313650773</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -3074,16 +3074,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.2950798822070655</v>
+        <v>0.2617632573633273</v>
       </c>
       <c r="O10" s="5">
         <v>9</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1240706597048703</v>
+        <v>0.1203688125000105</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1240706597048703</v>
+        <v>0.1203688125000105</v>
       </c>
       <c r="R10" s="5">
         <v>9</v>
@@ -3133,16 +3133,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.3297385735547351</v>
+        <v>0.2776976554299324</v>
       </c>
       <c r="O11" s="5">
         <v>8</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1552625156944364</v>
+        <v>0.1544102396354832</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1576517265917552</v>
+        <v>0.1501878012598326</v>
       </c>
       <c r="R11" s="5">
         <v>8</v>
@@ -3192,16 +3192,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.403139963703623</v>
+        <v>0.3312702208204144</v>
       </c>
       <c r="O12" s="5">
         <v>8</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2066145938815633</v>
+        <v>0.2050229329796373</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2039972099810576</v>
+        <v>0.1932228736059898</v>
       </c>
       <c r="R12" s="5">
         <v>8</v>
@@ -3251,16 +3251,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.3739909529840083</v>
+        <v>0.4579161083402141</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3288937425830081</v>
+        <v>0.3195687253212074</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3288937425830081</v>
+        <v>0.3195687253212074</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -3310,16 +3310,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.148558168547077</v>
+        <v>-0.1992381418847344</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1661468055314187</v>
+        <v>0.1605156973827901</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1661468055314187</v>
+        <v>0.1605156973827901</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -3426,16 +3426,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>0.1811218398757875</v>
+        <v>0.1548749753858374</v>
       </c>
       <c r="O16" s="5">
         <v>9</v>
       </c>
       <c r="P16" s="4">
-        <v>0.07779903942031788</v>
+        <v>0.07488272114365675</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.07779903942031788</v>
+        <v>0.07488272114365675</v>
       </c>
       <c r="R16" s="5">
         <v>9</v>
@@ -3485,16 +3485,16 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>0.4384400999535956</v>
+        <v>0.4422538896410515</v>
       </c>
       <c r="O17" s="5">
         <v>9</v>
       </c>
       <c r="P17" s="4">
-        <v>0.07488378931855284</v>
+        <v>0.07446003490883552</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.07488378931855284</v>
+        <v>0.07446003490883552</v>
       </c>
       <c r="R17" s="5">
         <v>9</v>
@@ -3544,16 +3544,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.005709728768872917</v>
+        <v>0.0722176849671996</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2623981662962954</v>
+        <v>0.2550083933853702</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2623981662962954</v>
+        <v>0.2550083933853702</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -3726,16 +3726,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.179531712446102</v>
+        <v>0.1225094901583859</v>
       </c>
       <c r="O3" s="5">
         <v>81</v>
       </c>
       <c r="P3" s="4">
-        <v>0.176559434086856</v>
+        <v>0.1725171118282287</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.176559434086856</v>
+        <v>0.1725171118282287</v>
       </c>
       <c r="R3" s="5">
         <v>81</v>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.355350139321308</v>
+        <v>0.3122587942335713</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.248923224020644</v>
+        <v>0.2479656385742498</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.248923224020644</v>
+        <v>0.2479656385742498</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -3844,13 +3844,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.6674230117666358</v>
+        <v>0.5881219967958309</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3321831003553947</v>
+        <v>0.3320923642597131</v>
       </c>
       <c r="Q5" s="4">
         <v>0.4553608064838269</v>
@@ -3903,16 +3903,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.4849325057769989</v>
+        <v>0.5043715600178693</v>
       </c>
       <c r="O6" s="5">
         <v>36</v>
       </c>
       <c r="P6" s="4">
-        <v>0.4782430478148693</v>
+        <v>0.4782430478148691</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.4782430478148693</v>
+        <v>0.4782430478148691</v>
       </c>
       <c r="R6" s="5">
         <v>36</v>
@@ -3962,16 +3962,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2397569608697287</v>
+        <v>0.2152914087909537</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1337374755996053</v>
+        <v>0.1320369897262084</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1337374755996053</v>
+        <v>0.1320369897262084</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.2097778828674866</v>
+        <v>0.2112159675371821</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -4080,16 +4080,16 @@
         <v>5</v>
       </c>
       <c r="N9" s="4">
-        <v>1.77488509491411</v>
+        <v>2.006274133841288</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5637119297940942</v>
+        <v>0.5380020365799633</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5637119297940942</v>
+        <v>0.5380020365799633</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -4310,16 +4310,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.7922333925154325</v>
+        <v>0.8355529063413769</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3025934268214325</v>
+        <v>0.2977801475074386</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3025934268214325</v>
+        <v>0.2977801475074386</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -4369,16 +4369,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.259475344207486</v>
+        <v>0.2088353909738743</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1673862697653083</v>
+        <v>0.161759608294907</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1673862697653083</v>
+        <v>0.161759608294907</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -4428,16 +4428,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.3871322600205633</v>
+        <v>0.3814504945443851</v>
       </c>
       <c r="O15" s="5">
         <v>9</v>
       </c>
       <c r="P15" s="4">
-        <v>0.1196329611960491</v>
+        <v>0.1190016539209182</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.1196329611960491</v>
+        <v>0.1190016539209182</v>
       </c>
       <c r="R15" s="5">
         <v>9</v>
@@ -4487,16 +4487,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>0.1297145726114039</v>
+        <v>0.1371365851691273</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
       </c>
       <c r="P16" s="4">
-        <v>0.05503916165021204</v>
+        <v>0.05256515746430424</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.05623026172035595</v>
+        <v>0.05474585920881125</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -4546,16 +4546,16 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>0.2917022229224698</v>
+        <v>0.2984042337586228</v>
       </c>
       <c r="O17" s="5">
         <v>9</v>
       </c>
       <c r="P17" s="4">
-        <v>0.07770147283393598</v>
+        <v>0.07695680496325233</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.07770147283393598</v>
+        <v>0.07695680496325233</v>
       </c>
       <c r="R17" s="5">
         <v>9</v>
@@ -4605,16 +4605,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.7042015841984431</v>
+        <v>0.8023193678025677</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2820709994364875</v>
+        <v>0.2711690234804737</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2820709994364875</v>
+        <v>0.2711690234804737</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -4787,22 +4787,22 @@
         <v>9</v>
       </c>
       <c r="N3" s="4">
-        <v>2.062909760873067</v>
+        <v>0.3305636394628948</v>
       </c>
       <c r="O3" s="5">
         <v>72</v>
       </c>
       <c r="P3" s="4">
-        <v>4.528061035805235</v>
+        <v>3.666022642465523</v>
       </c>
       <c r="Q3" s="4">
-        <v>1.70964912652373</v>
+        <v>0.1354352441893046</v>
       </c>
       <c r="R3" s="5">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="S3" s="5">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -4846,16 +4846,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2600489139963053</v>
+        <v>-0.3066489278027404</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2198884516008883</v>
+        <v>0.2176359044123283</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2198884516008883</v>
+        <v>0.2176359044123283</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -4905,16 +4905,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5224834450923481</v>
+        <v>0.5514112940820723</v>
       </c>
       <c r="O5" s="5">
         <v>11</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3959247794988678</v>
+        <v>0.3862821631689598</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2473150774383519</v>
+        <v>0.2446852729847406</v>
       </c>
       <c r="R5" s="5">
         <v>11</v>
@@ -4964,13 +4964,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>1.112591970550662</v>
+        <v>1.133542318315179</v>
       </c>
       <c r="O6" s="5">
         <v>18</v>
       </c>
       <c r="P6" s="4">
-        <v>27.60789628701608</v>
+        <v>27.59742111313382</v>
       </c>
       <c r="Q6" s="4">
         <v>0.4018555549674596</v>
@@ -5023,16 +5023,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2024761255263559</v>
+        <v>0.1752738702709991</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1360221172846045</v>
+        <v>0.1334714525788585</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1360221172846045</v>
+        <v>0.1334714525788585</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -5082,7 +5082,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.09167114498389069</v>
+        <v>0.08223370326173551</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -5414,16 +5414,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.07025774094456791</v>
+        <v>0.02006689656741401</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1697901710852864</v>
+        <v>0.164213410598936</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1697901710852864</v>
+        <v>0.164213410598936</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -5526,16 +5526,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.2441489859228227</v>
+        <v>-0.2485281613915902</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
       </c>
       <c r="P16" s="4">
-        <v>0.08242578070962736</v>
+        <v>0.07999290544920099</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.04080243907810882</v>
+        <v>0.03992660398435532</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -5638,16 +5638,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.6182706367685474</v>
+        <v>0.7149569809266723</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2803285503317591</v>
+        <v>0.2695856232030786</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2803285503317591</v>
+        <v>0.2695856232030786</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -5820,16 +5820,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.09989227798948977</v>
+        <v>-0.09706841569580327</v>
       </c>
       <c r="O3" s="5">
         <v>63</v>
       </c>
       <c r="P3" s="4">
-        <v>1.016999682905769</v>
+        <v>1.016337295454163</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1438005240972036</v>
+        <v>0.1437557008861927</v>
       </c>
       <c r="R3" s="5">
         <v>63</v>
@@ -5879,16 +5879,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.07186944215739478</v>
+        <v>0.115265159294438</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1517651061066334</v>
+        <v>0.1487539430183464</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1517651061066334</v>
+        <v>0.1487539430183464</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -5938,16 +5938,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.7736762168500281</v>
+        <v>0.7875776059765656</v>
       </c>
       <c r="O5" s="5">
         <v>25</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2732056626436142</v>
+        <v>0.270888764455858</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2914662970197676</v>
+        <v>0.2909102414547061</v>
       </c>
       <c r="R5" s="5">
         <v>25</v>
@@ -5997,20 +5997,22 @@
         <v>9</v>
       </c>
       <c r="N6" s="4">
-        <v>11.94281232463559</v>
+        <v>1.150631231569832</v>
       </c>
       <c r="O6" s="5">
         <v>27</v>
       </c>
       <c r="P6" s="4">
-        <v>17.55119143132766</v>
-      </c>
-      <c r="Q6" s="4"/>
+        <v>17.57145539344911</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.4992618013678939</v>
+      </c>
       <c r="R6" s="5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S6" s="5">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -6054,16 +6056,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.297331116167632</v>
+        <v>0.2995746455932604</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1343688321792585</v>
+        <v>0.1342857384968278</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1343688321792585</v>
+        <v>0.1342857384968278</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -6113,7 +6115,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.0006248831533163468</v>
+        <v>-0.006675445908186362</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -6172,16 +6174,16 @@
         <v>3</v>
       </c>
       <c r="N9" s="4">
-        <v>1.676806594869876</v>
+        <v>1.814620767656379</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.4992025626186991</v>
+        <v>0.4838898767535322</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.4992025626186991</v>
+        <v>0.4838898767535322</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -6231,16 +6233,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.19675497022349</v>
+        <v>-0.236535387656204</v>
       </c>
       <c r="O10" s="5">
         <v>9</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1051753809625864</v>
+        <v>0.1007553345811737</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1051753809625864</v>
+        <v>0.1007553345811737</v>
       </c>
       <c r="R10" s="5">
         <v>9</v>
@@ -6290,16 +6292,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.2002382712328625</v>
+        <v>-0.2582291634177238</v>
       </c>
       <c r="O11" s="5">
         <v>8</v>
       </c>
       <c r="P11" s="4">
-        <v>0.150332125442429</v>
+        <v>0.1463688577995457</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1460023563982737</v>
+        <v>0.1342948187769224</v>
       </c>
       <c r="R11" s="5">
         <v>8</v>
@@ -6406,16 +6408,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.4538893633572722</v>
+        <v>0.4714048778714641</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.2816775862003885</v>
+        <v>0.2797314179210338</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.2816775862003885</v>
+        <v>0.2797314179210338</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -6465,16 +6467,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.2095963402555488</v>
+        <v>0.1653076802588203</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1535254793203607</v>
+        <v>0.1486045170985019</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1535254793203607</v>
+        <v>0.1486045170985019</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -6577,16 +6579,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.1618624656119513</v>
+        <v>-0.196682963525376</v>
       </c>
       <c r="O16" s="5">
         <v>9</v>
       </c>
       <c r="P16" s="4">
-        <v>0.06337788252530437</v>
+        <v>0.05950893831270163</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.06337788252530437</v>
+        <v>0.05950893831270163</v>
       </c>
       <c r="R16" s="5">
         <v>9</v>
@@ -6636,16 +6638,16 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>-0.03561476641332067</v>
+        <v>-0.03936594525885084</v>
       </c>
       <c r="O17" s="5">
         <v>9</v>
       </c>
       <c r="P17" s="4">
-        <v>0.06961255033177637</v>
+        <v>0.06919575268227302</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.06961255033177637</v>
+        <v>0.06919575268227302</v>
       </c>
       <c r="R17" s="5">
         <v>9</v>
@@ -6695,16 +6697,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>1.021800174817186</v>
+        <v>1.090697509033362</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2613768281984523</v>
+        <v>0.2537215688410994</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2613768281984523</v>
+        <v>0.2537215688410994</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -6877,16 +6879,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.240389394804966</v>
+        <v>-0.2196893186938382</v>
       </c>
       <c r="O3" s="5">
         <v>63</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6959782016309531</v>
+        <v>0.6911226282221701</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1401892263928824</v>
+        <v>0.1398606537561978</v>
       </c>
       <c r="R3" s="5">
         <v>63</v>
@@ -6936,16 +6938,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1874294016502495</v>
+        <v>-0.2051191438854971</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1267516969932552</v>
+        <v>0.1263585916102496</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1267516969932552</v>
+        <v>0.1263585916102496</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -6995,13 +6997,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.454447958219677</v>
+        <v>0.4621365527343642</v>
       </c>
       <c r="O5" s="5">
         <v>26</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2869766291039178</v>
+        <v>0.286549484964213</v>
       </c>
       <c r="Q5" s="4">
         <v>0.3126449066030813</v>
@@ -7054,16 +7056,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.6751379588454749</v>
+        <v>0.7176135543359123</v>
       </c>
       <c r="O6" s="5">
         <v>18</v>
       </c>
       <c r="P6" s="4">
-        <v>16.61171708922117</v>
+        <v>16.58701570009984</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2293010330755615</v>
+        <v>0.2223738503233431</v>
       </c>
       <c r="R6" s="5">
         <v>18</v>
@@ -7113,16 +7115,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.1218530740879923</v>
+        <v>-0.104371578959956</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1875451078309974</v>
+        <v>0.1868976450484775</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1875451078309974</v>
+        <v>0.1868976450484775</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -7172,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.2431724905751914</v>
+        <v>-0.2466817017382681</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -7231,16 +7233,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>1.047790142504425</v>
+        <v>1.314254556718879</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5833500747955895</v>
+        <v>0.5537429176606502</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5833500747955895</v>
+        <v>0.5537429176606502</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -7290,16 +7292,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1304792676410247</v>
+        <v>-0.1813748651952665</v>
       </c>
       <c r="O10" s="5">
         <v>9</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1108803784608985</v>
+        <v>0.1052253120659827</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1108803784608985</v>
+        <v>0.1052253120659827</v>
       </c>
       <c r="R10" s="5">
         <v>9</v>
@@ -7349,16 +7351,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.119471116539259</v>
+        <v>-0.184924033412841</v>
       </c>
       <c r="O11" s="5">
         <v>8</v>
       </c>
       <c r="P11" s="4">
-        <v>0.149121859753003</v>
+        <v>0.143983188515149</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1469447058321727</v>
+        <v>0.1329820860803892</v>
       </c>
       <c r="R11" s="5">
         <v>8</v>
@@ -7408,16 +7410,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.07159664078339271</v>
+        <v>-0.1747321620700859</v>
       </c>
       <c r="O12" s="5">
         <v>9</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2104185453795337</v>
+        <v>0.1989590430143456</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.2104185453795337</v>
+        <v>0.1989590430143456</v>
       </c>
       <c r="R12" s="5">
         <v>9</v>
@@ -7467,16 +7469,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.112860514073418</v>
+        <v>0.1801756298245891</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3153463868369626</v>
+        <v>0.3078669295312769</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3153463868369626</v>
+        <v>0.3078669295312769</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -7526,16 +7528,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.1026320169997979</v>
+        <v>0.05138365376956244</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1641729116240837</v>
+        <v>0.1584786490429464</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1641729116240837</v>
+        <v>0.1584786490429464</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -7585,16 +7587,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.1057763618174998</v>
+        <v>-0.1085500470996976</v>
       </c>
       <c r="O15" s="5">
         <v>9</v>
       </c>
       <c r="P15" s="4">
-        <v>0.121132745200639</v>
+        <v>0.1208245579470615</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.121132745200639</v>
+        <v>0.1208245579470615</v>
       </c>
       <c r="R15" s="5">
         <v>9</v>
@@ -7644,16 +7646,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.4445578120203714</v>
+        <v>-0.4815225936523291</v>
       </c>
       <c r="O16" s="5">
         <v>9</v>
       </c>
       <c r="P16" s="4">
-        <v>0.06282055996429936</v>
+        <v>0.05871336200519295</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.06282055996429936</v>
+        <v>0.05871336200519295</v>
       </c>
       <c r="R16" s="5">
         <v>9</v>
@@ -7703,16 +7705,16 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>-0.2459781544748441</v>
+        <v>-0.2359124998242805</v>
       </c>
       <c r="O17" s="5">
         <v>9</v>
       </c>
       <c r="P17" s="4">
-        <v>0.08058586692513077</v>
+        <v>0.07946746085284594</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.08058586692513077</v>
+        <v>0.07946746085284594</v>
       </c>
       <c r="R17" s="5">
         <v>9</v>
@@ -7762,16 +7764,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.3959230593556242</v>
+        <v>0.4890286743470824</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2777029083323378</v>
+        <v>0.2673578399999536</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2777029083323378</v>
+        <v>0.2673578399999536</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -7944,16 +7946,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3034934376811375</v>
+        <v>0.3039554013265899</v>
       </c>
       <c r="O3" s="5">
         <v>81</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1550024933491064</v>
+        <v>0.1549967900942243</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1550024933491064</v>
+        <v>0.1549967900942243</v>
       </c>
       <c r="R3" s="5">
         <v>81</v>
@@ -8003,16 +8005,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4018144719724326</v>
+        <v>0.3868785364245459</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1186526599772136</v>
+        <v>0.1174480985521929</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1186526599772136</v>
+        <v>0.1174480985521929</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -8062,16 +8064,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>1.253219171511013</v>
+        <v>1.595463172584232</v>
       </c>
       <c r="O5" s="5">
         <v>13</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7653100521503737</v>
+        <v>0.9686724479020382</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.7569090787137267</v>
+        <v>0.7145578650503327</v>
       </c>
       <c r="R5" s="5">
         <v>13</v>
@@ -8121,16 +8123,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.064351058041071</v>
+        <v>-0.996055207260131</v>
       </c>
       <c r="O6" s="5">
         <v>36</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2778564433147722</v>
+        <v>0.2710920468582231</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2778564433147722</v>
+        <v>0.2710920468582231</v>
       </c>
       <c r="R6" s="5">
         <v>36</v>
@@ -8180,16 +8182,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.1113489903908392</v>
+        <v>0.07949470119659985</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1354076311711077</v>
+        <v>0.1329846155099709</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1354076311711077</v>
+        <v>0.1329846155099709</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -8239,7 +8241,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.405162137768405</v>
+        <v>0.4169267774881291</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -8298,16 +8300,16 @@
         <v>8</v>
       </c>
       <c r="N9" s="4">
-        <v>2.792432877032064</v>
+        <v>3.039369855943789</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5706581531376357</v>
+        <v>0.5432207110363328</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5706581531376357</v>
+        <v>0.5432207110363328</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -8524,16 +8526,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>1.219003405851295</v>
+        <v>1.269677010744999</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3067761513844231</v>
+        <v>0.3011457508406781</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3067761513844231</v>
+        <v>0.3011457508406781</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -8583,16 +8585,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.5248606977164196</v>
+        <v>0.4721610342360236</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1601535172911042</v>
+        <v>0.1542979991266158</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1601535172911042</v>
+        <v>0.1542979991266158</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -8805,16 +8807,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>1.447111197151813</v>
+        <v>1.546539884788672</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2833056625249253</v>
+        <v>0.2722580305652744</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2833056625249253</v>
+        <v>0.2722580305652744</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -8987,16 +8989,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1649459364839042</v>
+        <v>-0.1810701122031588</v>
       </c>
       <c r="O3" s="5">
         <v>81</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1296770577001169</v>
+        <v>0.1293714973123539</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1296770577001169</v>
+        <v>0.1293714973123539</v>
       </c>
       <c r="R3" s="5">
         <v>81</v>
@@ -9046,16 +9048,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1651177419962709</v>
+        <v>-0.1624469068731003</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.121768440797539</v>
+        <v>0.121709088905913</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.121768440797539</v>
+        <v>0.121709088905913</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -9105,16 +9107,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1561223717172133</v>
+        <v>-0.0999583414144638</v>
       </c>
       <c r="O5" s="5">
         <v>28</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4573665568425752</v>
+        <v>0.4488952899706646</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.5278819898361033</v>
+        <v>0.4849395789615996</v>
       </c>
       <c r="R5" s="5">
         <v>28</v>
@@ -9164,16 +9166,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.5355923318548429</v>
+        <v>-0.465562104431001</v>
       </c>
       <c r="O6" s="5">
         <v>36</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2752187559631327</v>
+        <v>0.2661631117930552</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2752187559631327</v>
+        <v>0.2661631117930552</v>
       </c>
       <c r="R6" s="5">
         <v>36</v>
@@ -9223,16 +9225,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.5783104682287311</v>
+        <v>-0.6221537269805939</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1362512526096708</v>
+        <v>0.1346274282114537</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1362512526096708</v>
+        <v>0.1346274282114537</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -9282,7 +9284,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.3749159931920776</v>
+        <v>-0.3806101198977565</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -9341,16 +9343,16 @@
         <v>5</v>
       </c>
       <c r="N9" s="4">
-        <v>1.880377172703188</v>
+        <v>2.134367738786636</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5757715664421208</v>
+        <v>0.5475503924328488</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5757715664421208</v>
+        <v>0.5475503924328488</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -9400,16 +9402,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.099095677596962</v>
+        <v>0.04280249533945835</v>
       </c>
       <c r="O10" s="5">
         <v>9</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1109375753723752</v>
+        <v>0.1046827773437637</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1109375753723752</v>
+        <v>0.1046827773437637</v>
       </c>
       <c r="R10" s="5">
         <v>9</v>
@@ -9459,16 +9461,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.1621892604498539</v>
+        <v>0.1565003229411843</v>
       </c>
       <c r="O11" s="5">
         <v>7</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1478518634767458</v>
+        <v>0.1472981149337455</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.09546615730260778</v>
+        <v>0.09312878417341608</v>
       </c>
       <c r="R11" s="5">
         <v>7</v>
@@ -9518,16 +9520,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.2194740951870386</v>
+        <v>0.2110530470129675</v>
       </c>
       <c r="O12" s="5">
         <v>5</v>
       </c>
       <c r="P12" s="4">
-        <v>0.217941735026964</v>
+        <v>0.2207487510849878</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.137652654094029</v>
+        <v>0.1359684444592148</v>
       </c>
       <c r="R12" s="5">
         <v>5</v>
@@ -9577,16 +9579,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.834370884645886</v>
+        <v>0.8928002988996582</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3121434363240408</v>
+        <v>0.3056512791847328</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3121434363240408</v>
+        <v>0.3056512791847328</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -9636,16 +9638,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.1527405027514656</v>
+        <v>0.1004630719519213</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1590240828585913</v>
+        <v>0.1532154794364197</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1590240828585913</v>
+        <v>0.1532154794364197</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -9695,13 +9697,13 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.3165414039792165</v>
+        <v>-0.2854988047577152</v>
       </c>
       <c r="O15" s="5">
         <v>6</v>
       </c>
       <c r="P15" s="4">
-        <v>0.1198171064690859</v>
+        <v>0.1199927451404036</v>
       </c>
       <c r="Q15" s="4">
         <v>0.1261263667444936</v>
@@ -9754,16 +9756,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.2122414504871147</v>
+        <v>-0.2314472845171309</v>
       </c>
       <c r="O16" s="5">
         <v>9</v>
       </c>
       <c r="P16" s="4">
-        <v>0.06383814223366183</v>
+        <v>0.06170416067477112</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.06383814223366183</v>
+        <v>0.06170416067477112</v>
       </c>
       <c r="R16" s="5">
         <v>9</v>
@@ -9813,16 +9815,16 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>-0.3708120175365206</v>
+        <v>-0.3466812775435226</v>
       </c>
       <c r="O17" s="5">
         <v>8</v>
       </c>
       <c r="P17" s="4">
-        <v>0.08443893990750596</v>
+        <v>0.07762382104098266</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.07222547263244961</v>
+        <v>0.06757480640673563</v>
       </c>
       <c r="R17" s="5">
         <v>8</v>
@@ -9872,16 +9874,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.9611363422586336</v>
+        <v>1.060827848381876</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.284312895661892</v>
+        <v>0.2732360616481984</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.284312895661892</v>
+        <v>0.2732360616481984</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -10054,16 +10056,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2884030987033709</v>
+        <v>0.2687923810498205</v>
       </c>
       <c r="O3" s="5">
         <v>81</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1556568103554895</v>
+        <v>0.1548133834148577</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1556568103554895</v>
+        <v>0.1548133834148577</v>
       </c>
       <c r="R3" s="5">
         <v>81</v>
@@ -10113,16 +10115,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4015178673391014</v>
+        <v>0.3915707302741254</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1102978616825739</v>
+        <v>0.1098622289493101</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1102978616825739</v>
+        <v>0.1098622289493101</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -10172,16 +10174,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>1.165719467872184</v>
+        <v>1.427660838752445</v>
       </c>
       <c r="O5" s="5">
         <v>13</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6059440038808775</v>
+        <v>0.763364352324144</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6649930991731671</v>
+        <v>0.6374916386894431</v>
       </c>
       <c r="R5" s="5">
         <v>13</v>
@@ -10231,16 +10233,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1074144271032826</v>
+        <v>-0.05472920483126487</v>
       </c>
       <c r="O6" s="5">
         <v>36</v>
       </c>
       <c r="P6" s="4">
-        <v>0.2735981031591385</v>
+        <v>0.2676881873476057</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2735981031591385</v>
+        <v>0.2676881873476057</v>
       </c>
       <c r="R6" s="5">
         <v>36</v>
@@ -10290,16 +10292,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.1924861972101616</v>
+        <v>0.1780539538766419</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1346688455804532</v>
+        <v>0.1339087742045641</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1346688455804532</v>
+        <v>0.1339087742045641</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -10349,7 +10351,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.4099633515097075</v>
+        <v>0.423273909490689</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -10408,16 +10410,16 @@
         <v>8</v>
       </c>
       <c r="N9" s="4">
-        <v>2.747670265643086</v>
+        <v>2.973040853563646</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5586638972239806</v>
+        <v>0.5336227207883629</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5586638972239806</v>
+        <v>0.5336227207883629</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -10638,16 +10640,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>1.182965219036245</v>
+        <v>1.224627820223759</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3018389559008739</v>
+        <v>0.2972097779911501</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3018389559008739</v>
+        <v>0.2972097779911501</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -10697,16 +10699,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.4408926875027797</v>
+        <v>0.3882708345747687</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1583672823530361</v>
+        <v>0.1525204098054793</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1583672823530361</v>
+        <v>0.1525204098054793</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -10919,16 +10921,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>1.021616354092697</v>
+        <v>1.114098530990759</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2779475817198415</v>
+        <v>0.2676717842867234</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2779475817198415</v>
+        <v>0.2676717842867234</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -11101,16 +11103,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.07277680152968706</v>
+        <v>-0.1296978117899528</v>
       </c>
       <c r="O3" s="5">
         <v>81</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4191765645899605</v>
+        <v>0.3743954974202297</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4191765645899605</v>
+        <v>0.3743954974202297</v>
       </c>
       <c r="R3" s="5">
         <v>81</v>
@@ -11160,16 +11162,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.142658086577168</v>
+        <v>0.1340918716680903</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1179868981786133</v>
+        <v>0.1177965378473004</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1179868981786133</v>
+        <v>0.1177965378473004</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -11219,22 +11221,22 @@
         <v>8</v>
       </c>
       <c r="N5" s="4">
-        <v>1.797513294708287</v>
+        <v>1.470177444574155</v>
       </c>
       <c r="O5" s="5">
         <v>28</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7339766448147663</v>
+        <v>0.6125121230457873</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.786763545135903</v>
+        <v>0.6683576117604894</v>
       </c>
       <c r="R5" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -11278,20 +11280,22 @@
         <v>9</v>
       </c>
       <c r="N6" s="4">
-        <v>10.98799013756511</v>
+        <v>-0.0006428399351534608</v>
       </c>
       <c r="O6" s="5">
         <v>27</v>
       </c>
       <c r="P6" s="4">
-        <v>13.23012239937384</v>
-      </c>
-      <c r="Q6" s="4"/>
+        <v>13.27072811501792</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2425893124696737</v>
+      </c>
       <c r="R6" s="5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S6" s="5">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -11335,16 +11339,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.3012943848292763</v>
+        <v>-0.3615141762036274</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1371803845296259</v>
+        <v>0.1349500218861314</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1371803845296259</v>
+        <v>0.1349500218861314</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -11394,7 +11398,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.02157183887731939</v>
+        <v>0.01652411234986673</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -11451,16 +11455,16 @@
         <v>9</v>
       </c>
       <c r="N9" s="4">
-        <v>4.491857673666055</v>
+        <v>4.753286157670914</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5793396034989093</v>
+        <v>0.5502919941650362</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5793396034989093</v>
+        <v>0.5502919941650362</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -11510,16 +11514,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>1.266963919192404</v>
+        <v>1.271410198501087</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1007391577499775</v>
+        <v>0.1000430561588435</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.07092998393825985</v>
+        <v>0.07062687810300616</v>
       </c>
       <c r="R10" s="5">
         <v>6</v>
@@ -11681,16 +11685,16 @@
         <v>9</v>
       </c>
       <c r="N13" s="4">
-        <v>2.760008249033398</v>
+        <v>2.847263423174866</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3240894257208778</v>
+        <v>0.3143944063718259</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3240894257208778</v>
+        <v>0.3143944063718259</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -11740,16 +11744,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.8886384941438131</v>
+        <v>0.8366398011541918</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1608544723288212</v>
+        <v>0.1550768397744188</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1608544723288212</v>
+        <v>0.1550768397744188</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -11856,16 +11860,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>0.6182577482145319</v>
+        <v>0.5978485891248368</v>
       </c>
       <c r="O16" s="5">
         <v>9</v>
       </c>
       <c r="P16" s="4">
-        <v>0.07133103182633881</v>
+        <v>0.06906334748303936</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.07133103182633881</v>
+        <v>0.06906334748303936</v>
       </c>
       <c r="R16" s="5">
         <v>9</v>
@@ -11968,16 +11972,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.8316886171745408</v>
+        <v>0.9317527980278726</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2863019188469627</v>
+        <v>0.2751836765299258</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2863019188469627</v>
+        <v>0.2751836765299258</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -12114,13 +12118,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>3.676417118090066</v>
+        <v>3.672355204644197</v>
       </c>
       <c r="I3" s="4">
-        <v>0.207813168472494</v>
+        <v>0.204721607502543</v>
       </c>
       <c r="J3" s="4">
-        <v>4.635256316134533</v>
+        <v>4.63615352299375</v>
       </c>
       <c r="K3" s="4">
         <v>70.46739926739923</v>
@@ -12164,13 +12168,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3119853182401922</v>
+        <v>0.3066139122630705</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3206412104480611</v>
+        <v>0.3154906695626912</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3195873693497258</v>
+        <v>0.3147868480637206</v>
       </c>
       <c r="K4" s="4">
         <v>79.05630559916277</v>
@@ -12196,13 +12200,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="3">
-        <v>79.38461538461539</v>
+        <v>84.92307692307692</v>
       </c>
       <c r="C5" s="3">
         <v>9.230769230769232</v>
       </c>
       <c r="D5" s="3">
-        <v>11.38461538461539</v>
+        <v>5.846153846153846</v>
       </c>
       <c r="E5" s="3">
         <v>1.538461538461539</v>
@@ -12211,16 +12215,16 @@
         <v>1.538461538461539</v>
       </c>
       <c r="G5" s="3">
-        <v>8.307692307692308</v>
+        <v>2.769230769230769</v>
       </c>
       <c r="H5" s="4">
-        <v>3.988302746053301</v>
+        <v>3.982263795924549</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2463881650179819</v>
+        <v>0.2434295696703503</v>
       </c>
       <c r="J5" s="4">
-        <v>4.714504923043368</v>
+        <v>4.719219808628608</v>
       </c>
       <c r="K5" s="4">
         <v>75.8919937205653</v>
@@ -12264,13 +12268,13 @@
         <v>12.30769230769231</v>
       </c>
       <c r="H6" s="4">
-        <v>1.169274253375839</v>
+        <v>1.156796435773502</v>
       </c>
       <c r="I6" s="4">
-        <v>0.232368363047985</v>
+        <v>0.2123642169284871</v>
       </c>
       <c r="J6" s="4">
-        <v>1.267181729380794</v>
+        <v>1.259323985387435</v>
       </c>
       <c r="K6" s="4">
         <v>72.69314495028785</v>
@@ -12314,13 +12318,13 @@
         <v>2.769230769230769</v>
       </c>
       <c r="H7" s="4">
-        <v>2.837698665779868</v>
+        <v>2.733750955870578</v>
       </c>
       <c r="I7" s="4">
-        <v>0.388333082742467</v>
+        <v>0.1889264017143472</v>
       </c>
       <c r="J7" s="4">
-        <v>4.400265226948393</v>
+        <v>4.298330805543242</v>
       </c>
       <c r="K7" s="4">
         <v>73.20858189429634</v>
@@ -12364,13 +12368,13 @@
         <v>0.3076923076923077</v>
       </c>
       <c r="H8" s="4">
-        <v>1.331435569330564</v>
+        <v>1.331025025369569</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1795461015195767</v>
+        <v>0.1759121641760351</v>
       </c>
       <c r="J8" s="4">
-        <v>2.709460161521013</v>
+        <v>2.708727225946083</v>
       </c>
       <c r="K8" s="4">
         <v>77.20983778126624</v>
@@ -12414,13 +12418,13 @@
         <v>11.07692307692308</v>
       </c>
       <c r="H9" s="4">
-        <v>0.7210533185877154</v>
+        <v>0.7147864569057994</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3136678403001363</v>
+        <v>0.3075124914460893</v>
       </c>
       <c r="J9" s="4">
-        <v>0.7345956992174117</v>
+        <v>0.7329430816242445</v>
       </c>
       <c r="K9" s="4">
         <v>75.96828885400299</v>
@@ -12464,13 +12468,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.2521495817165362</v>
+        <v>0.2494486119638004</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2522801379280675</v>
+        <v>0.2492530088960985</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2709688931967972</v>
+        <v>0.2696081791709271</v>
       </c>
       <c r="K10" s="4">
         <v>76.64018838304554</v>
@@ -12496,13 +12500,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>60</v>
+        <v>61.23076923076923</v>
       </c>
       <c r="C11" s="3">
         <v>27.38461538461539</v>
       </c>
       <c r="D11" s="3">
-        <v>12.61538461538461</v>
+        <v>11.38461538461539</v>
       </c>
       <c r="E11" s="3">
         <v>8.307692307692308</v>
@@ -12511,16 +12515,16 @@
         <v>0.3076923076923077</v>
       </c>
       <c r="G11" s="3">
-        <v>4</v>
+        <v>2.769230769230769</v>
       </c>
       <c r="H11" s="4">
-        <v>4.443487473174744</v>
+        <v>4.225369454883746</v>
       </c>
       <c r="I11" s="4">
-        <v>0.6687062045680661</v>
+        <v>0.189499572996306</v>
       </c>
       <c r="J11" s="4">
-        <v>5.506291484087891</v>
+        <v>5.292127183558426</v>
       </c>
       <c r="K11" s="4">
         <v>71.7978021978021</v>
@@ -12546,13 +12550,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>75.38461538461539</v>
+        <v>80.92307692307692</v>
       </c>
       <c r="C12" s="3">
         <v>11.69230769230769</v>
       </c>
       <c r="D12" s="3">
-        <v>12.92307692307692</v>
+        <v>7.384615384615385</v>
       </c>
       <c r="E12" s="3">
         <v>4</v>
@@ -12561,16 +12565,16 @@
         <v>0.6153846153846154</v>
       </c>
       <c r="G12" s="3">
-        <v>8.307692307692308</v>
+        <v>2.769230769230769</v>
       </c>
       <c r="H12" s="4">
-        <v>2.316875920720729</v>
+        <v>2.317097944921171</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1756859295036974</v>
+        <v>0.1955694523062095</v>
       </c>
       <c r="J12" s="4">
-        <v>2.940255759676661</v>
+        <v>2.944099911483184</v>
       </c>
       <c r="K12" s="4">
         <v>83.3432757718472</v>
@@ -12614,13 +12618,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>2.138667177793532</v>
+        <v>2.1323246649609</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1843927803228771</v>
+        <v>0.1808883547486988</v>
       </c>
       <c r="J13" s="4">
-        <v>3.998169401407681</v>
+        <v>3.991354126198699</v>
       </c>
       <c r="K13" s="4">
         <v>76.22553636839348</v>
@@ -12664,13 +12668,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.2723421043471068</v>
+        <v>0.2923657978519665</v>
       </c>
       <c r="I14" s="4">
-        <v>0.2175706121963804</v>
+        <v>0.2121367012975571</v>
       </c>
       <c r="J14" s="4">
-        <v>0.2774554011332552</v>
+        <v>0.2940345978974411</v>
       </c>
       <c r="K14" s="4">
         <v>66.85400313971725</v>
@@ -12714,13 +12718,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.2018354398153195</v>
+        <v>0.1978920640292746</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2002366747825709</v>
+        <v>0.1930655636968237</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2094980487016584</v>
+        <v>0.2094943976494414</v>
       </c>
       <c r="K15" s="4">
         <v>82.36295133437982</v>
@@ -12764,13 +12768,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.2511316353006522</v>
+        <v>0.266312544142102</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2101182059183716</v>
+        <v>0.2057894116454557</v>
       </c>
       <c r="J16" s="4">
-        <v>0.2677696084332946</v>
+        <v>0.2777182521441638</v>
       </c>
       <c r="K16" s="4">
         <v>66.61758241758271</v>
@@ -12796,13 +12800,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="3">
-        <v>75.69230769230769</v>
+        <v>80.92307692307692</v>
       </c>
       <c r="C17" s="3">
         <v>12.30769230769231</v>
       </c>
       <c r="D17" s="3">
-        <v>12</v>
+        <v>6.769230769230769</v>
       </c>
       <c r="E17" s="3">
         <v>2.769230769230769</v>
@@ -12811,16 +12815,16 @@
         <v>0</v>
       </c>
       <c r="G17" s="3">
-        <v>9.230769230769232</v>
+        <v>4</v>
       </c>
       <c r="H17" s="4">
-        <v>1.852108775675724</v>
+        <v>1.830156806220564</v>
       </c>
       <c r="I17" s="4">
-        <v>0.3429095795554818</v>
+        <v>0.3061582269038345</v>
       </c>
       <c r="J17" s="4">
-        <v>3.09346302139364</v>
+        <v>3.078089905012259</v>
       </c>
       <c r="K17" s="4">
         <v>79.89450549450559</v>
@@ -13791,13 +13795,13 @@
         <v>19</v>
       </c>
       <c r="B5" s="5">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="C5" s="5">
         <v>30</v>
       </c>
       <c r="D5" s="5">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E5" s="5">
         <v>5</v>
@@ -13806,7 +13810,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="5">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H5" s="5">
         <v>5</v>
@@ -14055,13 +14059,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C11" s="5">
         <v>89</v>
       </c>
       <c r="D11" s="5">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E11" s="5">
         <v>27</v>
@@ -14070,7 +14074,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H11" s="5">
         <v>27</v>
@@ -14099,13 +14103,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="C12" s="5">
         <v>38</v>
       </c>
       <c r="D12" s="5">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E12" s="5">
         <v>13</v>
@@ -14114,7 +14118,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="5">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H12" s="5">
         <v>13</v>
@@ -14319,13 +14323,13 @@
         <v>31</v>
       </c>
       <c r="B17" s="5">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C17" s="5">
         <v>40</v>
       </c>
       <c r="D17" s="5">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="E17" s="5">
         <v>9</v>
@@ -14334,7 +14338,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="5">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H17" s="5">
         <v>9</v>
@@ -14517,16 +14521,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3792904543946547</v>
+        <v>-0.3881844969164945</v>
       </c>
       <c r="O3" s="5">
         <v>63</v>
       </c>
       <c r="P3" s="4">
-        <v>2.463244149828668</v>
+        <v>2.465110800728313</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1581771536692663</v>
+        <v>0.1580359783911419</v>
       </c>
       <c r="R3" s="5">
         <v>63</v>
@@ -14576,16 +14580,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.118326679906136</v>
+        <v>-0.08868768337404731</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1368447081529794</v>
+        <v>0.1361860637855996</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1368447081529794</v>
+        <v>0.1361860637855996</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -14635,16 +14639,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3681618258266148</v>
+        <v>0.3914444276367703</v>
       </c>
       <c r="O5" s="5">
         <v>28</v>
       </c>
       <c r="P5" s="4">
-        <v>0.349381712449027</v>
+        <v>0.3494940117632612</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3853505265167332</v>
+        <v>0.3838318683628802</v>
       </c>
       <c r="R5" s="5">
         <v>28</v>
@@ -14694,16 +14698,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.5790811266379011</v>
+        <v>0.6306821320263225</v>
       </c>
       <c r="O6" s="5">
         <v>18</v>
       </c>
       <c r="P6" s="4">
-        <v>26.42839045354373</v>
+        <v>26.40080042965823</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.2332990068378746</v>
+        <v>0.2297199644552994</v>
       </c>
       <c r="R6" s="5">
         <v>18</v>
@@ -14753,16 +14757,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2682528445137148</v>
+        <v>0.2577969472704353</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2115751361949304</v>
+        <v>0.2111878807414756</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2115751361949304</v>
+        <v>0.2111878807414756</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -14812,7 +14816,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.1941947579599649</v>
+        <v>0.189271438520521</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -14871,16 +14875,16 @@
         <v>5</v>
       </c>
       <c r="N9" s="4">
-        <v>1.763373096063453</v>
+        <v>2.023956094804817</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5866180929765309</v>
+        <v>0.5576644264497127</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5866180929765309</v>
+        <v>0.5576644264497127</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -14930,16 +14934,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1351711350781054</v>
+        <v>-0.1368634983984123</v>
       </c>
       <c r="O10" s="5">
         <v>6</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1041834628754475</v>
+        <v>0.1044252749501058</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.06549461565103976</v>
+        <v>0.06501115210287385</v>
       </c>
       <c r="R10" s="5">
         <v>6</v>
@@ -14989,16 +14993,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1559495125820149</v>
+        <v>-0.1880453006249923</v>
       </c>
       <c r="O11" s="5">
         <v>5</v>
       </c>
       <c r="P11" s="4">
-        <v>0.1446753669635301</v>
+        <v>0.1477649189432352</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1158806567765532</v>
+        <v>0.1094614991679577</v>
       </c>
       <c r="R11" s="5">
         <v>5</v>
@@ -15048,16 +15052,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.1282270350455974</v>
+        <v>-0.1610371506054946</v>
       </c>
       <c r="O12" s="5">
         <v>6</v>
       </c>
       <c r="P12" s="4">
-        <v>0.1943292890617714</v>
+        <v>0.1922628757617701</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1363807498090258</v>
+        <v>0.1254960672200506</v>
       </c>
       <c r="R12" s="5">
         <v>6</v>
@@ -15107,16 +15111,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.1646073063368729</v>
+        <v>0.2247999584378704</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3094789114921516</v>
+        <v>0.3027908390364852</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3094789114921516</v>
+        <v>0.3027908390364852</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -15166,16 +15170,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.3311819258034789</v>
+        <v>-0.3820365275048516</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1700550806176215</v>
+        <v>0.1644045693174689</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1700550806176215</v>
+        <v>0.1644045693174689</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -15278,16 +15282,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.2110661927278414</v>
+        <v>-0.2342115306347523</v>
       </c>
       <c r="O16" s="5">
         <v>6</v>
       </c>
       <c r="P16" s="4">
-        <v>0.06569702270904226</v>
+        <v>0.0676284259754804</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.0502574472222174</v>
+        <v>0.04261467230467986</v>
       </c>
       <c r="R16" s="5">
         <v>6</v>
@@ -15390,16 +15394,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.2429216449506492</v>
+        <v>0.3420861930321735</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.285404264066327</v>
+        <v>0.2743859809461576</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.285404264066327</v>
+        <v>0.2743859809461576</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -15572,16 +15576,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1448724897972782</v>
+        <v>-0.1796480585155962</v>
       </c>
       <c r="O3" s="5">
         <v>81</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2483928271567336</v>
+        <v>0.2466656857194566</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2483928271567336</v>
+        <v>0.2466656857194566</v>
       </c>
       <c r="R3" s="5">
         <v>81</v>
@@ -15631,16 +15635,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1942061053788194</v>
+        <v>-0.3013633710546912</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4487062146454747</v>
+        <v>0.4407176965053461</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4487062146454747</v>
+        <v>0.4407176965053461</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -15690,16 +15694,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.04902773956531965</v>
+        <v>-0.05365623123046248</v>
       </c>
       <c r="O5" s="5">
         <v>35</v>
       </c>
       <c r="P5" s="4">
-        <v>0.458177763521586</v>
+        <v>0.4436373295415762</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.44442594672056</v>
+        <v>0.4324038995067152</v>
       </c>
       <c r="R5" s="5">
         <v>35</v>
@@ -15749,16 +15753,16 @@
         <v>9</v>
       </c>
       <c r="N6" s="4">
-        <v>1.45759917361701</v>
+        <v>1.356089555605209</v>
       </c>
       <c r="O6" s="5">
         <v>36</v>
       </c>
       <c r="P6" s="4">
-        <v>0.5277019336887933</v>
+        <v>0.5251871095169379</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.5277019336887933</v>
+        <v>0.5251871095169379</v>
       </c>
       <c r="R6" s="5">
         <v>36</v>
@@ -15808,16 +15812,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.4079881016977788</v>
+        <v>0.4435812935546863</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.2107606049798074</v>
+        <v>0.2094423386147368</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.2107606049798074</v>
+        <v>0.2094423386147368</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -15867,7 +15871,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.03237606289160553</v>
+        <v>0.02874897758302097</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -15926,16 +15930,16 @@
         <v>5</v>
       </c>
       <c r="N9" s="4">
-        <v>1.77375331117847</v>
+        <v>2.03527048689466</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.581418613508456</v>
+        <v>0.5523611495399905</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.581418613508456</v>
+        <v>0.5523611495399905</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -15985,13 +15989,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.3213467325976183</v>
+        <v>-0.3504251945117005</v>
       </c>
       <c r="O10" s="5">
         <v>8</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1117184417079089</v>
+        <v>0.1084875014952331</v>
       </c>
       <c r="Q10" s="4">
         <v>0.09841333353516291</v>
@@ -16044,16 +16048,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.3931064622091248</v>
+        <v>-0.4619884656635804</v>
       </c>
       <c r="O11" s="5">
         <v>9</v>
       </c>
       <c r="P11" s="4">
-        <v>0.145472523656438</v>
+        <v>0.1378189677170541</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.145472523656438</v>
+        <v>0.1378189677170541</v>
       </c>
       <c r="R11" s="5">
         <v>9</v>
@@ -16103,13 +16107,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.3670357609618833</v>
+        <v>-0.4149583330467976</v>
       </c>
       <c r="O12" s="5">
         <v>8</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2097634377880869</v>
+        <v>0.2044387075564297</v>
       </c>
       <c r="Q12" s="4">
         <v>0.1869317885400363</v>
@@ -16162,16 +16166,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.02522220212666879</v>
+        <v>0.05698379632849537</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3251745540341076</v>
+        <v>0.3160405542057561</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3251745540341076</v>
+        <v>0.3160405542057561</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -16221,16 +16225,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.1709936747319729</v>
+        <v>-0.2232135141991876</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1628011747443817</v>
+        <v>0.1569989703591356</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1628011747443817</v>
+        <v>0.1569989703591356</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -16333,13 +16337,13 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.3058383138110052</v>
+        <v>-0.3009452815429512</v>
       </c>
       <c r="O16" s="5">
         <v>8</v>
       </c>
       <c r="P16" s="4">
-        <v>0.06772646585257963</v>
+        <v>0.06827013610458563</v>
       </c>
       <c r="Q16" s="4">
         <v>0.06016560684812688</v>
@@ -16449,16 +16453,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.6123507034494556</v>
+        <v>0.6721603691407836</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2576972230205612</v>
+        <v>0.2510517046104137</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2576972230205612</v>
+        <v>0.2510517046104137</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -16631,16 +16635,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2840440280777986</v>
+        <v>0.1476937869276753</v>
       </c>
       <c r="O3" s="5">
         <v>81</v>
       </c>
       <c r="P3" s="4">
-        <v>0.320870653449373</v>
+        <v>0.2978442686183026</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.320870653449373</v>
+        <v>0.2978442686183026</v>
       </c>
       <c r="R3" s="5">
         <v>81</v>
@@ -16690,16 +16694,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.09188969064995357</v>
+        <v>0.0686584259164249</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1206428368083434</v>
+        <v>0.119913459315613</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1206428368083434</v>
+        <v>0.119913459315613</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -16749,16 +16753,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4246864533222361</v>
+        <v>0.2818173481817894</v>
       </c>
       <c r="O5" s="5">
         <v>25</v>
       </c>
       <c r="P5" s="4">
-        <v>0.377004297298234</v>
+        <v>0.3690671247904314</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4497473147125975</v>
+        <v>0.4440325505069797</v>
       </c>
       <c r="R5" s="5">
         <v>25</v>
@@ -16808,20 +16812,22 @@
         <v>9</v>
       </c>
       <c r="N6" s="4">
-        <v>29.57141424985439</v>
+        <v>0.7684316483981277</v>
       </c>
       <c r="O6" s="5">
         <v>27</v>
       </c>
       <c r="P6" s="4">
-        <v>34.07311272161935</v>
-      </c>
-      <c r="Q6" s="4"/>
+        <v>34.09544184167235</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3441130180723274</v>
+      </c>
       <c r="R6" s="5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S6" s="5">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -16865,16 +16871,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.272889988743745</v>
+        <v>0.2873812901013721</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1453982354325588</v>
+        <v>0.1448615205674615</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1453982354325588</v>
+        <v>0.1448615205674615</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -16924,7 +16930,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1541459053539008</v>
+        <v>-0.1591058488673269</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -16983,16 +16989,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>1.374047907797546</v>
+        <v>1.647255037422383</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5953064519574632</v>
+        <v>0.5649501042213703</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5953064519574632</v>
+        <v>0.5649501042213703</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -17156,16 +17162,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.2476057081606086</v>
+        <v>-0.235601123738661</v>
       </c>
       <c r="O12" s="5">
         <v>5</v>
       </c>
       <c r="P12" s="4">
-        <v>0.2068759208741034</v>
+        <v>0.2002067073063548</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1059775062229483</v>
+        <v>0.1035765893385587</v>
       </c>
       <c r="R12" s="5">
         <v>5</v>
@@ -17215,16 +17221,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.3520202438190709</v>
+        <v>0.4306601559819683</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3219410980847481</v>
+        <v>0.3132033300666485</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3219410980847481</v>
+        <v>0.3132033300666485</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -17274,16 +17280,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.2501677641238871</v>
+        <v>0.2260385771489837</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.1579591023870156</v>
+        <v>0.1552780816120263</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.1579591023870156</v>
+        <v>0.1552780816120263</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -17390,16 +17396,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.1523282059747544</v>
+        <v>-0.1700474042719406</v>
       </c>
       <c r="O16" s="5">
         <v>9</v>
       </c>
       <c r="P16" s="4">
-        <v>0.06155120436403649</v>
+        <v>0.05958240455323802</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.06155120436403649</v>
+        <v>0.05958240455323802</v>
       </c>
       <c r="R16" s="5">
         <v>9</v>
@@ -17449,16 +17455,16 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>0.07484571032952975</v>
+        <v>0.08866661985803148</v>
       </c>
       <c r="O17" s="5">
         <v>9</v>
       </c>
       <c r="P17" s="4">
-        <v>0.07985498961987626</v>
+        <v>0.07831933300559829</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.07985498961987626</v>
+        <v>0.07831933300559829</v>
       </c>
       <c r="R17" s="5">
         <v>9</v>
@@ -17508,16 +17514,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.6191380201161647</v>
+        <v>0.7199172050427478</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.3025615214054278</v>
+        <v>0.291363834191363</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.3025615214054278</v>
+        <v>0.291363834191363</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -17690,16 +17696,16 @@
         <v>4</v>
       </c>
       <c r="N3" s="4">
-        <v>0.436837253500579</v>
+        <v>0.277142686616223</v>
       </c>
       <c r="O3" s="5">
         <v>74</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4100046199511727</v>
+        <v>0.3846616944520393</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.217770925746886</v>
+        <v>0.1707397613754187</v>
       </c>
       <c r="R3" s="5">
         <v>70</v>
@@ -17749,16 +17755,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.02614054683932289</v>
+        <v>-0.02909333494264388</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1711351484951796</v>
+        <v>0.1710695309817724</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1711351484951796</v>
+        <v>0.1710695309817724</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -17808,16 +17814,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4616462402036309</v>
+        <v>0.3080165315820267</v>
       </c>
       <c r="O5" s="5">
         <v>33</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4806927430934315</v>
+        <v>0.4428607807481796</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4819126526576618</v>
+        <v>0.4452968667241023</v>
       </c>
       <c r="R5" s="5">
         <v>33</v>
@@ -17867,13 +17873,13 @@
         <v>20</v>
       </c>
       <c r="N6" s="4">
-        <v>9.935978131789277</v>
+        <v>9.493071497890782</v>
       </c>
       <c r="O6" s="5">
         <v>36</v>
       </c>
       <c r="P6" s="4">
-        <v>8.306948842648666</v>
+        <v>8.306948842648662</v>
       </c>
       <c r="Q6" s="4"/>
       <c r="R6" s="5">
@@ -17924,16 +17930,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2767510363472109</v>
+        <v>0.2877265079516604</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1547144621039145</v>
+        <v>0.1538380667954339</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1547144621039145</v>
+        <v>0.1538380667954339</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -17983,7 +17989,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.1221126913808554</v>
+        <v>-0.1282784579931473</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -18042,16 +18048,16 @@
         <v>8</v>
       </c>
       <c r="N9" s="4">
-        <v>2.705989876662411</v>
+        <v>2.881652628007942</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5324657808743898</v>
+        <v>0.512947697391553</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5324657808743898</v>
+        <v>0.512947697391553</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -18101,16 +18107,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.07142248610246485</v>
+        <v>0.02427477554692814</v>
       </c>
       <c r="O10" s="5">
         <v>9</v>
       </c>
       <c r="P10" s="4">
-        <v>0.1073417522492376</v>
+        <v>0.1021031177430669</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1073417522492376</v>
+        <v>0.1021031177430669</v>
       </c>
       <c r="R10" s="5">
         <v>9</v>
@@ -18160,16 +18166,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.07352426153219464</v>
+        <v>-0.01151636996092975</v>
       </c>
       <c r="O11" s="5">
         <v>9</v>
       </c>
       <c r="P11" s="4">
-        <v>0.144891182631168</v>
+        <v>0.1354422235763764</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.144891182631168</v>
+        <v>0.1354422235763764</v>
       </c>
       <c r="R11" s="5">
         <v>9</v>
@@ -18219,16 +18225,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.1091572790299754</v>
+        <v>-0.005950298476591342</v>
       </c>
       <c r="O12" s="5">
         <v>9</v>
       </c>
       <c r="P12" s="4">
-        <v>0.1935099232971649</v>
+        <v>0.1807201924631019</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.1935099232971649</v>
+        <v>0.1807201924631019</v>
       </c>
       <c r="R12" s="5">
         <v>9</v>
@@ -18278,16 +18284,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.5744109087674284</v>
+        <v>0.6137617504300579</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3015563975068121</v>
+        <v>0.2971840817665199</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3015563975068121</v>
+        <v>0.2971840817665199</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -18337,16 +18343,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.2352397949132094</v>
+        <v>0.1782166158056953</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.152823056978178</v>
+        <v>0.1464871481884542</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.152823056978178</v>
+        <v>0.1464871481884542</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -18449,16 +18455,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.01074132608558405</v>
+        <v>-0.04509261623533689</v>
       </c>
       <c r="O16" s="5">
         <v>9</v>
       </c>
       <c r="P16" s="4">
-        <v>0.06529964223667589</v>
+        <v>0.0614828322200367</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.06529964223667589</v>
+        <v>0.0614828322200367</v>
       </c>
       <c r="R16" s="5">
         <v>9</v>
@@ -18561,16 +18567,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>1.26278872076479</v>
+        <v>1.323052388412634</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2601632187620403</v>
+        <v>0.2534672556900577</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2601632187620403</v>
+        <v>0.2534672556900577</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
@@ -18743,16 +18749,16 @@
         <v>9</v>
       </c>
       <c r="N3" s="4">
-        <v>1.06028641475626</v>
+        <v>0.1540896704320289</v>
       </c>
       <c r="O3" s="5">
         <v>72</v>
       </c>
       <c r="P3" s="4">
-        <v>1.572240136757649</v>
+        <v>1.159352298747478</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.9418973252772941</v>
+        <v>0.1521281780287224</v>
       </c>
       <c r="R3" s="5">
         <v>63</v>
@@ -18802,16 +18808,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1503662055986925</v>
+        <v>0.1562075506030283</v>
       </c>
       <c r="O4" s="5">
         <v>45</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1112511601765137</v>
+        <v>0.1109727203064321</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1112511601765137</v>
+        <v>0.1109727203064321</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -18861,16 +18867,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.7076307168663524</v>
+        <v>0.6217170354785537</v>
       </c>
       <c r="O5" s="5">
         <v>18</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3143574372359919</v>
+        <v>0.3203995727962459</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4477311661231866</v>
+        <v>0.4475708499739837</v>
       </c>
       <c r="R5" s="5">
         <v>18</v>
@@ -18920,13 +18926,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.4224579220887475</v>
+        <v>0.4230778330760927</v>
       </c>
       <c r="O6" s="5">
         <v>18</v>
       </c>
       <c r="P6" s="4">
-        <v>20.89749242077801</v>
+        <v>20.89718246528434</v>
       </c>
       <c r="Q6" s="4">
         <v>0.2517828214062617</v>
@@ -18979,16 +18985,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.155827428909512</v>
+        <v>0.1506750371362386</v>
       </c>
       <c r="O7" s="5">
         <v>27</v>
       </c>
       <c r="P7" s="4">
-        <v>0.1358314054455519</v>
+        <v>0.1356405761206158</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.1358314054455519</v>
+        <v>0.1356405761206158</v>
       </c>
       <c r="R7" s="5">
         <v>27</v>
@@ -19038,7 +19044,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.1631118417001993</v>
+        <v>0.1623118282617355</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
@@ -19097,16 +19103,16 @@
         <v>3</v>
       </c>
       <c r="N9" s="4">
-        <v>1.704994664531335</v>
+        <v>1.934158121172004</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5607135670313148</v>
+        <v>0.5352509607379071</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5607135670313148</v>
+        <v>0.5352509607379071</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -19156,16 +19162,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>0.216649156584009</v>
+        <v>0.2405838904980442</v>
       </c>
       <c r="O10" s="5">
         <v>5</v>
       </c>
       <c r="P10" s="4">
-        <v>0.09582917163021672</v>
+        <v>0.08785092699220501</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.07922505625938128</v>
+        <v>0.07443810947657425</v>
       </c>
       <c r="R10" s="5">
         <v>5</v>
@@ -19329,16 +19335,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.7801383800130881</v>
+        <v>0.8344648754300579</v>
       </c>
       <c r="O13" s="5">
         <v>9</v>
       </c>
       <c r="P13" s="4">
-        <v>0.3092102814526069</v>
+        <v>0.3031740041840547</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3092102814526069</v>
+        <v>0.3031740041840547</v>
       </c>
       <c r="R13" s="5">
         <v>9</v>
@@ -19388,16 +19394,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>0.2257367482416599</v>
+        <v>0.1736656819678046</v>
       </c>
       <c r="O14" s="5">
         <v>9</v>
       </c>
       <c r="P14" s="4">
-        <v>0.161053195686222</v>
+        <v>0.1552675216557936</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.161053195686222</v>
+        <v>0.1552675216557936</v>
       </c>
       <c r="R14" s="5">
         <v>9</v>
@@ -19447,16 +19453,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>0.3028368431385549</v>
+        <v>0.2976904161571383</v>
       </c>
       <c r="O15" s="5">
         <v>9</v>
       </c>
       <c r="P15" s="4">
-        <v>0.120463053902896</v>
+        <v>0.1198912286827386</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.120463053902896</v>
+        <v>0.1198912286827386</v>
       </c>
       <c r="R15" s="5">
         <v>9</v>
@@ -19506,16 +19512,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>0.134415626664088</v>
+        <v>0.1371347289258438</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
       </c>
       <c r="P16" s="4">
-        <v>0.05780592345572081</v>
+        <v>0.05689955603513555</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.05056807937813346</v>
+        <v>0.05002425892578231</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -19565,16 +19571,16 @@
         <v>0</v>
       </c>
       <c r="N17" s="4">
-        <v>0.2128854217784111</v>
+        <v>0.2219007631151726</v>
       </c>
       <c r="O17" s="5">
         <v>9</v>
       </c>
       <c r="P17" s="4">
-        <v>0.07807946953653125</v>
+        <v>0.07707776494355774</v>
       </c>
       <c r="Q17" s="4">
-        <v>0.07807946953653125</v>
+        <v>0.07707776494355774</v>
       </c>
       <c r="R17" s="5">
         <v>9</v>
@@ -19624,16 +19630,16 @@
         <v>0</v>
       </c>
       <c r="N18" s="4">
-        <v>0.733442122245571</v>
+        <v>0.8315249652337116</v>
       </c>
       <c r="O18" s="5">
         <v>9</v>
       </c>
       <c r="P18" s="4">
-        <v>0.2823103326562793</v>
+        <v>0.2714122389909303</v>
       </c>
       <c r="Q18" s="4">
-        <v>0.2823103326562793</v>
+        <v>0.2714122389909303</v>
       </c>
       <c r="R18" s="5">
         <v>9</v>
